--- a/data/Type1/whole community/Tunberg_1998b.xlsx
+++ b/data/Type1/whole community/Tunberg_1998b.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29825"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://bangoroffice365-my.sharepoint.com/personal/lrm22dyy_bangor_ac_uk/Documents/Desktop/DGENV thresholds request/Data/Type 1/whole community/"/>
@@ -10,20 +10,39 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="8" documentId="8_{124B57FC-3CF0-469F-AB34-837D3180ADC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{207CBC12-931D-4F55-B066-10C14D23D174}"/>
   <bookViews>
-    <workbookView xWindow="120" yWindow="36" windowWidth="19680" windowHeight="15792" activeTab="1" xr2:uid="{45E8B3AD-A108-4A93-8C46-0879D30A8E4B}"/>
+    <workbookView xWindow="120" yWindow="36" windowWidth="19680" windowHeight="15792" firstSheet="1" activeTab="1" xr2:uid="{45E8B3AD-A108-4A93-8C46-0879D30A8E4B}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata and protocols" sheetId="3" r:id="rId1"/>
     <sheet name="Time series information" sheetId="1" r:id="rId2"/>
     <sheet name="Species information" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191028"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="27">
   <si>
+    <t>cl_name</t>
+  </si>
+  <si>
     <t>station</t>
   </si>
   <si>
@@ -57,6 +76,27 @@
     <t>assessment_unit</t>
   </si>
   <si>
+    <t>replicate</t>
+  </si>
+  <si>
+    <t>outcome</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>AphiaID</t>
+  </si>
+  <si>
+    <t>outcome_value</t>
+  </si>
+  <si>
+    <t>outcome_units</t>
+  </si>
+  <si>
+    <t>total_biomass</t>
+  </si>
+  <si>
     <t>Tunberg_1998b</t>
   </si>
   <si>
@@ -72,24 +112,6 @@
     <t>NA</t>
   </si>
   <si>
-    <t>replicate</t>
-  </si>
-  <si>
-    <t>outcome</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>AphiaID</t>
-  </si>
-  <si>
-    <t>outcome_value</t>
-  </si>
-  <si>
-    <t>outcome_units</t>
-  </si>
-  <si>
     <t>Biomass</t>
   </si>
   <si>
@@ -97,19 +119,13 @@
   </si>
   <si>
     <t>g/m2</t>
-  </si>
-  <si>
-    <t>cl_name</t>
-  </si>
-  <si>
-    <t>total_biomass</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -599,48 +615,48 @@
     </xf>
   </cellXfs>
   <cellStyles count="42">
-    <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
-    <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
-    <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
-    <cellStyle name="20% - Accent4" xfId="31" builtinId="42" customBuiltin="1"/>
-    <cellStyle name="20% - Accent5" xfId="35" builtinId="46" customBuiltin="1"/>
-    <cellStyle name="20% - Accent6" xfId="39" builtinId="50" customBuiltin="1"/>
-    <cellStyle name="40% - Accent1" xfId="20" builtinId="31" customBuiltin="1"/>
-    <cellStyle name="40% - Accent2" xfId="24" builtinId="35" customBuiltin="1"/>
-    <cellStyle name="40% - Accent3" xfId="28" builtinId="39" customBuiltin="1"/>
-    <cellStyle name="40% - Accent4" xfId="32" builtinId="43" customBuiltin="1"/>
-    <cellStyle name="40% - Accent5" xfId="36" builtinId="47" customBuiltin="1"/>
-    <cellStyle name="40% - Accent6" xfId="40" builtinId="51" customBuiltin="1"/>
-    <cellStyle name="60% - Accent1" xfId="21" builtinId="32" customBuiltin="1"/>
-    <cellStyle name="60% - Accent2" xfId="25" builtinId="36" customBuiltin="1"/>
-    <cellStyle name="60% - Accent3" xfId="29" builtinId="40" customBuiltin="1"/>
-    <cellStyle name="60% - Accent4" xfId="33" builtinId="44" customBuiltin="1"/>
-    <cellStyle name="60% - Accent5" xfId="37" builtinId="48" customBuiltin="1"/>
-    <cellStyle name="60% - Accent6" xfId="41" builtinId="52" customBuiltin="1"/>
-    <cellStyle name="Accent1" xfId="18" builtinId="29" customBuiltin="1"/>
-    <cellStyle name="Accent2" xfId="22" builtinId="33" customBuiltin="1"/>
-    <cellStyle name="Accent3" xfId="26" builtinId="37" customBuiltin="1"/>
-    <cellStyle name="Accent4" xfId="30" builtinId="41" customBuiltin="1"/>
-    <cellStyle name="Accent5" xfId="34" builtinId="45" customBuiltin="1"/>
-    <cellStyle name="Accent6" xfId="38" builtinId="49" customBuiltin="1"/>
-    <cellStyle name="Bad" xfId="7" builtinId="27" customBuiltin="1"/>
-    <cellStyle name="Calculation" xfId="11" builtinId="22" customBuiltin="1"/>
-    <cellStyle name="Check Cell" xfId="13" builtinId="23" customBuiltin="1"/>
-    <cellStyle name="Explanatory Text" xfId="16" builtinId="53" customBuiltin="1"/>
-    <cellStyle name="Good" xfId="6" builtinId="26" customBuiltin="1"/>
-    <cellStyle name="Heading 1" xfId="2" builtinId="16" customBuiltin="1"/>
-    <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
-    <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
-    <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
-    <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
-    <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent1" xfId="19" builtinId="30" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent2" xfId="23" builtinId="34" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent3" xfId="27" builtinId="38" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent4" xfId="31" builtinId="42" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent5" xfId="35" builtinId="46" customBuiltin="1"/>
+    <cellStyle name="20 % - Akzent6" xfId="39" builtinId="50" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent1" xfId="20" builtinId="31" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent2" xfId="24" builtinId="35" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent3" xfId="28" builtinId="39" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent4" xfId="32" builtinId="43" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent5" xfId="36" builtinId="47" customBuiltin="1"/>
+    <cellStyle name="40 % - Akzent6" xfId="40" builtinId="51" customBuiltin="1"/>
+    <cellStyle name="60 % - Akzent1" xfId="21" builtinId="32" customBuiltin="1"/>
+    <cellStyle name="60 % - Akzent2" xfId="25" builtinId="36" customBuiltin="1"/>
+    <cellStyle name="60 % - Akzent3" xfId="29" builtinId="40" customBuiltin="1"/>
+    <cellStyle name="60 % - Akzent4" xfId="33" builtinId="44" customBuiltin="1"/>
+    <cellStyle name="60 % - Akzent5" xfId="37" builtinId="48" customBuiltin="1"/>
+    <cellStyle name="60 % - Akzent6" xfId="41" builtinId="52" customBuiltin="1"/>
+    <cellStyle name="Akzent1" xfId="18" builtinId="29" customBuiltin="1"/>
+    <cellStyle name="Akzent2" xfId="22" builtinId="33" customBuiltin="1"/>
+    <cellStyle name="Akzent3" xfId="26" builtinId="37" customBuiltin="1"/>
+    <cellStyle name="Akzent4" xfId="30" builtinId="41" customBuiltin="1"/>
+    <cellStyle name="Akzent5" xfId="34" builtinId="45" customBuiltin="1"/>
+    <cellStyle name="Akzent6" xfId="38" builtinId="49" customBuiltin="1"/>
+    <cellStyle name="Ausgabe" xfId="10" builtinId="21" customBuiltin="1"/>
+    <cellStyle name="Berechnung" xfId="11" builtinId="22" customBuiltin="1"/>
+    <cellStyle name="Eingabe" xfId="9" builtinId="20" customBuiltin="1"/>
+    <cellStyle name="Ergebnis" xfId="17" builtinId="25" customBuiltin="1"/>
+    <cellStyle name="Erklärender Text" xfId="16" builtinId="53" customBuiltin="1"/>
+    <cellStyle name="Gut" xfId="6" builtinId="26" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Note" xfId="15" builtinId="10" customBuiltin="1"/>
-    <cellStyle name="Output" xfId="10" builtinId="21" customBuiltin="1"/>
-    <cellStyle name="Title" xfId="1" builtinId="15" customBuiltin="1"/>
-    <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
-    <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Notiz" xfId="15" builtinId="10" customBuiltin="1"/>
+    <cellStyle name="Schlecht" xfId="7" builtinId="27" customBuiltin="1"/>
+    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Überschrift" xfId="1" builtinId="15" customBuiltin="1"/>
+    <cellStyle name="Überschrift 1" xfId="2" builtinId="16" customBuiltin="1"/>
+    <cellStyle name="Überschrift 2" xfId="3" builtinId="17" customBuiltin="1"/>
+    <cellStyle name="Überschrift 3" xfId="4" builtinId="18" customBuiltin="1"/>
+    <cellStyle name="Überschrift 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Verknüpfte Zelle" xfId="12" builtinId="24" customBuiltin="1"/>
+    <cellStyle name="Warnender Text" xfId="14" builtinId="11" customBuiltin="1"/>
+    <cellStyle name="Zelle überprüfen" xfId="13" builtinId="23" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -973,112 +989,112 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B4EAE81-4CEE-4757-B013-3CBD2D5A8F8E}">
   <dimension ref="A1:A21"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
       <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
       <c r="A3" s="2" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
       <c r="A4" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="2"/>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A5" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A6" s="2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A7" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A8" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A9" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A10" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A11" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A12" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A13" s="2"/>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1">
       <c r="A16" s="3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
+    <row r="21" spans="1:1">
+      <c r="A21" s="1" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A19" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A20" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
-      <c r="A21" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1089,49 +1105,49 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BB2BD5B-245F-4057-AA9A-3EE965E176FB}">
   <dimension ref="A1:L13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B2">
         <v>1983</v>
@@ -1143,13 +1159,13 @@
         <v>56.906999999999996</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F2">
         <v>50</v>
       </c>
       <c r="G2" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H2">
         <v>0.1</v>
@@ -1158,18 +1174,18 @@
         <v>1</v>
       </c>
       <c r="J2" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="K2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="L2">
         <v>1.3023897209999999</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B3">
         <v>1984</v>
@@ -1181,13 +1197,13 @@
         <v>56.906999999999996</v>
       </c>
       <c r="E3" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F3">
         <v>50</v>
       </c>
       <c r="G3" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H3">
         <v>0.1</v>
@@ -1196,18 +1212,18 @@
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="K3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="L3">
         <v>1.142136206</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B4">
         <v>1985</v>
@@ -1219,13 +1235,13 @@
         <v>56.906999999999996</v>
       </c>
       <c r="E4" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F4">
         <v>50</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H4">
         <v>0.1</v>
@@ -1234,18 +1250,18 @@
         <v>1</v>
       </c>
       <c r="J4" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="K4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="L4">
         <v>0.49231856600000001</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B5">
         <v>1986</v>
@@ -1257,13 +1273,13 @@
         <v>56.906999999999996</v>
       </c>
       <c r="E5" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F5">
         <v>50</v>
       </c>
       <c r="G5" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H5">
         <v>0.1</v>
@@ -1272,18 +1288,18 @@
         <v>1</v>
       </c>
       <c r="J5" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="K5" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="L5">
         <v>2.0885388709999999</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B6">
         <v>1987</v>
@@ -1295,13 +1311,13 @@
         <v>56.906999999999996</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F6">
         <v>50</v>
       </c>
       <c r="G6" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H6">
         <v>0.1</v>
@@ -1310,18 +1326,18 @@
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="K6" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="L6">
         <v>2.4362448919999999</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>1988</v>
@@ -1333,13 +1349,13 @@
         <v>56.906999999999996</v>
       </c>
       <c r="E7" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F7">
         <v>50</v>
       </c>
       <c r="G7" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H7">
         <v>0.1</v>
@@ -1348,18 +1364,18 @@
         <v>1</v>
       </c>
       <c r="J7" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="K7" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="L7">
         <v>3.0226484079999998</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B8">
         <v>1989</v>
@@ -1371,13 +1387,13 @@
         <v>56.906999999999996</v>
       </c>
       <c r="E8" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F8">
         <v>50</v>
       </c>
       <c r="G8" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H8">
         <v>0.1</v>
@@ -1386,18 +1402,18 @@
         <v>1</v>
       </c>
       <c r="J8" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="K8" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="L8">
         <v>2.7400304320000002</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>1990</v>
@@ -1409,13 +1425,13 @@
         <v>56.906999999999996</v>
       </c>
       <c r="E9" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F9">
         <v>50</v>
       </c>
       <c r="G9" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H9">
         <v>0.1</v>
@@ -1424,18 +1440,18 @@
         <v>1</v>
       </c>
       <c r="J9" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="K9" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="L9">
         <v>2.3961947979999998</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B10">
         <v>1991</v>
@@ -1447,13 +1463,13 @@
         <v>56.906999999999996</v>
       </c>
       <c r="E10" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F10">
         <v>50</v>
       </c>
       <c r="G10" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H10">
         <v>0.1</v>
@@ -1462,18 +1478,18 @@
         <v>1</v>
       </c>
       <c r="J10" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="K10" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="L10">
         <v>1.7708394220000001</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B11">
         <v>1992</v>
@@ -1485,13 +1501,13 @@
         <v>56.906999999999996</v>
       </c>
       <c r="E11" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F11">
         <v>50</v>
       </c>
       <c r="G11" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H11">
         <v>0.1</v>
@@ -1500,18 +1516,18 @@
         <v>1</v>
       </c>
       <c r="J11" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="K11" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="L11">
         <v>1.739141217</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B12">
         <v>1993</v>
@@ -1523,13 +1539,13 @@
         <v>56.906999999999996</v>
       </c>
       <c r="E12" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F12">
         <v>50</v>
       </c>
       <c r="G12" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H12">
         <v>0.1</v>
@@ -1538,18 +1554,18 @@
         <v>1</v>
       </c>
       <c r="J12" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="K12" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="L12">
         <v>4.051400868</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B13">
         <v>1994</v>
@@ -1561,13 +1577,13 @@
         <v>56.906999999999996</v>
       </c>
       <c r="E13" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F13">
         <v>50</v>
       </c>
       <c r="G13" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="H13">
         <v>0.1</v>
@@ -1576,10 +1592,10 @@
         <v>1</v>
       </c>
       <c r="J13" t="s">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="K13" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="L13">
         <v>0.88012782000000001</v>
@@ -1596,37 +1612,37 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C81D4F0C-28F5-400C-88C3-9907C821AD80}">
   <dimension ref="A1:H13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8">
       <c r="A1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" t="s">
         <v>16</v>
       </c>
-      <c r="D1" t="s">
+      <c r="H1" t="s">
         <v>17</v>
       </c>
-      <c r="E1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B2">
         <v>1983</v>
@@ -1635,24 +1651,24 @@
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G2">
         <v>1.3023897209999999</v>
       </c>
       <c r="H2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
       <c r="A3" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B3">
         <v>1984</v>
@@ -1661,24 +1677,24 @@
         <v>1</v>
       </c>
       <c r="D3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G3">
         <v>1.142136206</v>
       </c>
       <c r="H3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B4">
         <v>1985</v>
@@ -1687,24 +1703,24 @@
         <v>1</v>
       </c>
       <c r="D4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G4">
         <v>0.49231856600000001</v>
       </c>
       <c r="H4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B5">
         <v>1986</v>
@@ -1713,24 +1729,24 @@
         <v>1</v>
       </c>
       <c r="D5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G5">
         <v>2.0885388709999999</v>
       </c>
       <c r="H5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B6">
         <v>1987</v>
@@ -1739,24 +1755,24 @@
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F6" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G6">
         <v>2.4362448919999999</v>
       </c>
       <c r="H6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B7">
         <v>1988</v>
@@ -1765,24 +1781,24 @@
         <v>1</v>
       </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G7">
         <v>3.0226484079999998</v>
       </c>
       <c r="H7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B8">
         <v>1989</v>
@@ -1791,24 +1807,24 @@
         <v>1</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F8" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G8">
         <v>2.7400304320000002</v>
       </c>
       <c r="H8" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B9">
         <v>1990</v>
@@ -1817,24 +1833,24 @@
         <v>1</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E9" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F9" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G9">
         <v>2.3961947979999998</v>
       </c>
       <c r="H9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B10">
         <v>1991</v>
@@ -1843,24 +1859,24 @@
         <v>1</v>
       </c>
       <c r="D10" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E10" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F10" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G10">
         <v>1.7708394220000001</v>
       </c>
       <c r="H10" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B11">
         <v>1992</v>
@@ -1869,24 +1885,24 @@
         <v>1</v>
       </c>
       <c r="D11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E11" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F11" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G11">
         <v>1.739141217</v>
       </c>
       <c r="H11" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B12">
         <v>1993</v>
@@ -1895,24 +1911,24 @@
         <v>1</v>
       </c>
       <c r="D12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F12" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G12">
         <v>4.051400868</v>
       </c>
       <c r="H12" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B13">
         <v>1994</v>
@@ -1921,19 +1937,19 @@
         <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E13" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F13" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G13">
         <v>0.88012782000000001</v>
       </c>
       <c r="H13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1945,21 +1961,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101008C3347BB67BB9B48B9267C5825329A8D" ma:contentTypeVersion="" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="946ead2bedc6697490567b3bc7a69b8e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9f31fc9b1d39c82eedb31998474f3939">
     <xsd:element name="properties">
@@ -2073,35 +2074,29 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19A77D7A-AE06-4E85-9531-7142CD543806}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BFCDB2B-34F3-4B32-AA3A-D1D30811F1A6}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF998BB5-17ED-497B-A0EF-260EC54BF0B8}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FF998BB5-17ED-497B-A0EF-260EC54BF0B8}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2BFCDB2B-34F3-4B32-AA3A-D1D30811F1A6}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19A77D7A-AE06-4E85-9531-7142CD543806}"/>
 </file>